--- a/ig/document/ValueSet-MedCom-ihe-core-HealthcareFacilityTypeCode-VS-TEMP.xlsx
+++ b/ig/document/ValueSet-MedCom-ihe-core-HealthcareFacilityTypeCode-VS-TEMP.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>2.0.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/ig/document/ValueSet-MedCom-ihe-core-HealthcareFacilityTypeCode-VS-TEMP.xlsx
+++ b/ig/document/ValueSet-MedCom-ihe-core-HealthcareFacilityTypeCode-VS-TEMP.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.1</t>
+    <t>2.0.2</t>
   </si>
   <si>
     <t>Name</t>
